--- a/jira_export_2026-08-04.xlsx
+++ b/jira_export_2026-08-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>23 h</t>
+          <t>32 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -2278,12 +2278,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -2325,22 +2325,22 @@
         <v>2</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="16" t="n">
@@ -2350,27 +2350,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2401,16 +2401,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>0</v>
@@ -2422,32 +2422,32 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -2473,16 +2473,16 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>1616</v>
+        <v>920</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
@@ -2494,27 +2494,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -2545,16 +2545,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1017.5</v>
+        <v>1616</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2566,27 +2566,27 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2601,32 +2601,32 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O26" s="13" t="n">
         <v>0</v>
@@ -2638,32 +2638,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2689,16 +2689,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O27" s="13" t="n">
         <v>0</v>
@@ -2710,32 +2710,32 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -2761,16 +2761,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>4174</v>
+        <v>171.4</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2782,27 +2782,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2833,16 +2833,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>344</v>
+        <v>4174</v>
       </c>
       <c r="O29" s="13" t="n">
         <v>0</v>
@@ -2854,32 +2854,32 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2905,16 +2905,16 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>514.2</v>
+        <v>344</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
@@ -2926,32 +2926,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>500</v>
+        <v>514.2</v>
       </c>
       <c r="O31" s="13" t="n">
         <v>0</v>
@@ -2998,27 +2998,27 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -3049,16 +3049,16 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O32" s="13" t="n">
         <v>0</v>
@@ -3070,32 +3070,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3121,16 +3121,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3142,32 +3142,32 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3214,12 +3214,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3286,27 +3286,27 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3337,16 +3337,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>1079</v>
+        <v>1207</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3358,32 +3358,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3409,16 +3409,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>500</v>
+        <v>1079</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3430,32 +3430,32 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3502,32 +3502,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3553,16 +3553,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3574,12 +3574,12 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3625,16 +3625,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3646,32 +3646,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3718,27 +3718,27 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -3769,16 +3769,16 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3790,32 +3790,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3841,16 +3841,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3862,28 +3862,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3893,12 +3897,12 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -3909,16 +3913,16 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3930,27 +3934,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr"/>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3981,16 +3981,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>0</v>
@@ -4002,12 +4002,12 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -4053,16 +4053,16 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O46" s="13" t="n">
         <v>0</v>
@@ -4074,32 +4074,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4109,34 +4109,34 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -4146,32 +4146,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4181,34 +4181,34 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="O48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="16" t="n">
@@ -4218,32 +4218,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4269,16 +4269,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4290,12 +4290,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -4341,16 +4341,16 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4362,32 +4362,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4413,16 +4413,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4434,27 +4434,27 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4557,16 +4557,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4578,32 +4578,32 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4629,16 +4629,16 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4650,12 +4650,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4697,14 +4697,22 @@
         <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr"/>
-      <c r="M55" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="O55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4714,27 +4722,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4744,7 +4752,7 @@
       </c>
       <c r="G56" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H56" s="15" t="inlineStr">
@@ -4754,29 +4762,21 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M56" s="15" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L56" s="15" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr"/>
       <c r="N56" s="16" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -4786,32 +4786,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4837,16 +4837,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4858,12 +4858,12 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4909,16 +4909,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4930,12 +4930,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4981,16 +4981,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -5002,12 +5002,12 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5053,16 +5053,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5074,12 +5074,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5114,27 +5114,27 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5146,32 +5146,32 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5197,16 +5197,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5218,27 +5218,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5269,16 +5269,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5341,16 +5341,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5362,32 +5362,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5397,32 +5397,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5434,32 +5434,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5469,34 +5469,34 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>725</v>
+      </c>
+      <c r="O66" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
@@ -5773,18 +5773,18 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
@@ -5794,12 +5794,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5809,11 +5809,13 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
@@ -5832,27 +5834,27 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5864,12 +5866,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5879,7 +5881,7 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E72" s="15" t="n">
@@ -5902,29 +5904,29 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="16" t="n">
@@ -5934,26 +5936,28 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
@@ -5972,23 +5976,23 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
@@ -6004,22 +6008,22 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E74" s="15" t="n">
@@ -6042,23 +6046,23 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K74" s="15" t="n">
         <v>0.12</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
@@ -6074,22 +6078,22 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -6112,23 +6116,23 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>0.12</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6144,22 +6148,22 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E76" s="15" t="n">
@@ -6177,34 +6181,34 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="16" t="n">
@@ -6214,22 +6218,22 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6252,23 +6256,23 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2.75</v>
+        <v>0.12</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6284,22 +6288,22 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E78" s="15" t="n">
@@ -6317,34 +6321,34 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
@@ -6354,22 +6358,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6377,7 +6381,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6387,34 +6391,34 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6424,12 +6428,12 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -6439,7 +6443,7 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E80" s="15" t="n">
@@ -6462,27 +6466,27 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>557.145</v>
+        <v>401</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
@@ -6494,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6509,7 +6513,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6522,33 +6526,33 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6564,22 +6568,22 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E82" s="15" t="n">
@@ -6592,70 +6596,546 @@
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18196</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Gentilly</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H82" s="15" t="inlineStr">
+      <c r="H83" s="11" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>19/12/2024</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
+      <c r="N83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-14798</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+      <c r="J86" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="K86" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L86" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
+      <c r="N86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>19/09/2023</t>
         </is>
       </c>
-      <c r="J82" s="15" t="n">
+      <c r="J88" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="K82" s="15" t="n">
+      <c r="K88" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L82" s="15" t="inlineStr">
+      <c r="L88" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-34532</t>
         </is>
       </c>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="M88" s="15" t="inlineStr">
         <is>
           <t>412263</t>
         </is>
       </c>
-      <c r="N82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="N88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
+      <c r="N89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B83" s="17" t="inlineStr"/>
-      <c r="C83" s="17" t="inlineStr"/>
-      <c r="D83" s="17" t="inlineStr"/>
-      <c r="E83" s="17" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr"/>
-      <c r="G83" s="17" t="inlineStr"/>
-      <c r="H83" s="17" t="inlineStr"/>
-      <c r="I83" s="17" t="inlineStr"/>
-      <c r="J83" s="17" t="inlineStr"/>
-      <c r="K83" s="17" t="inlineStr"/>
-      <c r="L83" s="17" t="inlineStr"/>
-      <c r="M83" s="17" t="inlineStr"/>
-      <c r="N83" s="18" t="n">
-        <v>61735.894</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="18" t="n">
+      <c r="B90" s="17" t="inlineStr"/>
+      <c r="C90" s="17" t="inlineStr"/>
+      <c r="D90" s="17" t="inlineStr"/>
+      <c r="E90" s="17" t="inlineStr"/>
+      <c r="F90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr"/>
+      <c r="H90" s="17" t="inlineStr"/>
+      <c r="I90" s="17" t="inlineStr"/>
+      <c r="J90" s="17" t="inlineStr"/>
+      <c r="K90" s="17" t="inlineStr"/>
+      <c r="L90" s="17" t="inlineStr"/>
+      <c r="M90" s="17" t="inlineStr"/>
+      <c r="N90" s="18" t="n">
+        <v>61735.89399999999</v>
+      </c>
+      <c r="O90" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6740,6 +7220,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7314,26 +7801,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7862,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
     </row>
   </sheetData>
@@ -7539,17 +8026,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -7563,7 +8050,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 0 commande(s)</t>
+          <t>Épics créées ce mois — 1 commande(s)</t>
         </is>
       </c>
     </row>
@@ -7613,6 +8100,114 @@
         <is>
           <t>Montant (€)</t>
         </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34929</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34925</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>00178034</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>0 commande(s)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-04.xlsx
+++ b/jira_export_2026-08-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>32 h</t>
+          <t>34 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1533,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>4.25</v>
@@ -7810,7 +7810,7 @@
         <v>0.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>6</v>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-04.xlsx
+++ b/jira_export_2026-08-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>34 h</t>
+          <t>50 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1533,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>5</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -5866,12 +5866,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E72" s="15" t="n">
@@ -5904,29 +5904,29 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="16" t="n">
@@ -5936,28 +5936,26 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v/>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
@@ -5976,29 +5974,29 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O73" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -6008,12 +6006,12 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6023,11 +6021,13 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
@@ -6046,23 +6046,23 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
@@ -6123,16 +6123,16 @@
         <v>11</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6148,22 +6148,22 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E76" s="15" t="n">
@@ -6186,23 +6186,23 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E78" s="15" t="n">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
@@ -6428,22 +6428,22 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E80" s="15" t="n">
@@ -6461,34 +6461,34 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
@@ -6498,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6531,34 +6531,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O81" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6568,22 +6568,22 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E82" s="15" t="n">
@@ -6599,36 +6599,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H82" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H82" s="15" t="inlineStr"/>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M82" s="15" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr"/>
       <c r="N82" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
@@ -6638,12 +6626,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6653,7 +6641,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6666,7 +6654,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6676,17 +6664,25 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr"/>
-      <c r="M83" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
@@ -6700,22 +6696,22 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E84" s="15" t="n">
@@ -6723,7 +6719,7 @@
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6733,32 +6729,32 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
@@ -6770,12 +6766,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6785,7 +6781,7 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6798,39 +6794,31 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M85" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
       <c r="N85" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6840,22 +6828,22 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E86" s="15" t="n">
@@ -6863,44 +6851,44 @@
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
@@ -6910,12 +6898,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6925,7 +6913,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6948,29 +6936,29 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6980,22 +6968,22 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E88" s="15" t="n">
@@ -7013,28 +7001,28 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
@@ -7050,12 +7038,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7065,13 +7053,11 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v/>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
@@ -7080,7 +7066,7 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -7090,52 +7076,194 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>19/09/2023</t>
+        </is>
+      </c>
+      <c r="J90" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K90" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L90" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K91" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="11" t="inlineStr"/>
-      <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
+      <c r="N91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B90" s="17" t="inlineStr"/>
-      <c r="C90" s="17" t="inlineStr"/>
-      <c r="D90" s="17" t="inlineStr"/>
-      <c r="E90" s="17" t="inlineStr"/>
-      <c r="F90" s="17" t="inlineStr"/>
-      <c r="G90" s="17" t="inlineStr"/>
-      <c r="H90" s="17" t="inlineStr"/>
-      <c r="I90" s="17" t="inlineStr"/>
-      <c r="J90" s="17" t="inlineStr"/>
-      <c r="K90" s="17" t="inlineStr"/>
-      <c r="L90" s="17" t="inlineStr"/>
-      <c r="M90" s="17" t="inlineStr"/>
-      <c r="N90" s="18" t="n">
+      <c r="B92" s="17" t="inlineStr"/>
+      <c r="C92" s="17" t="inlineStr"/>
+      <c r="D92" s="17" t="inlineStr"/>
+      <c r="E92" s="17" t="inlineStr"/>
+      <c r="F92" s="17" t="inlineStr"/>
+      <c r="G92" s="17" t="inlineStr"/>
+      <c r="H92" s="17" t="inlineStr"/>
+      <c r="I92" s="17" t="inlineStr"/>
+      <c r="J92" s="17" t="inlineStr"/>
+      <c r="K92" s="17" t="inlineStr"/>
+      <c r="L92" s="17" t="inlineStr"/>
+      <c r="M92" s="17" t="inlineStr"/>
+      <c r="N92" s="18" t="n">
         <v>61735.89399999999</v>
       </c>
-      <c r="O90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="18" t="n">
+      <c r="O92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7227,6 +7355,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7801,7 +7931,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>4.25</v>
@@ -7810,7 +7940,7 @@
         <v>0.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>6</v>
@@ -7820,7 +7950,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7992,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>13.25</v>
+        <v>25.75</v>
       </c>
     </row>
   </sheetData>
